--- a/GETFREELOOPBACKIP/free_ips_report.xlsx
+++ b/GETFREELOOPBACKIP/free_ips_report.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-31 16:49:41</t>
+          <t>Generated: 2026-04-15 14:34:12</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scanned: 2026-03-31 16:49:41</t>
+          <t>Scanned: 2026-04-15 14:34:12</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scanned: 2026-03-31 16:49:41</t>
+          <t>Scanned: 2026-04-15 14:34:12</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scanned: 2026-03-31 16:49:41</t>
+          <t>Scanned: 2026-04-15 14:34:12</t>
         </is>
       </c>
     </row>
